--- a/display/Col_Cards_Totals_v1.xlsx
+++ b/display/Col_Cards_Totals_v1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Col_Cards_Totals" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Col_Cards_Totals" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L253"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1996,149 +1996,149 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>ECONOMY IMPACT - TOTAL (mean per player)</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="6" t="n"/>
+      <c r="I39" s="6" t="n"/>
+      <c r="J39" s="6" t="n"/>
+      <c r="K39" s="6" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K40" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+      <c r="I40" s="7" t="n"/>
+      <c r="J40" s="7" t="n"/>
+      <c r="K40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -3223,149 +3223,149 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>ECONOMY IMPACT - FROM SET COMPLETIONS</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
-      <c r="I61" s="6" t="n"/>
-      <c r="J61" s="6" t="n"/>
-      <c r="K61" s="6" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="7" t="n"/>
-      <c r="F62" s="7" t="n"/>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n"/>
-      <c r="J62" s="7" t="n"/>
-      <c r="K62" s="7" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="n"/>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="6" t="n"/>
+      <c r="I63" s="6" t="n"/>
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="6" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="7" t="n"/>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n"/>
+      <c r="J64" s="7" t="n"/>
+      <c r="K64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -4450,149 +4450,149 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>ECONOMY IMPACT - FROM ALBUM COMPLETIONS</t>
         </is>
       </c>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="6" t="n"/>
-      <c r="H85" s="6" t="n"/>
-      <c r="I85" s="6" t="n"/>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="6" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="n"/>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
-      <c r="K86" s="7" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K87" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="6" t="n"/>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="6" t="n"/>
+      <c r="I87" s="6" t="n"/>
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="6" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K88" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A88" s="7" t="n"/>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
+      <c r="K88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="8" t="inlineStr">
@@ -5677,161 +5677,151 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>UNLIMITED BOOSTERS IN MINUTES</t>
         </is>
       </c>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6" t="n"/>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="6" t="n"/>
-      <c r="G109" s="6" t="n"/>
-      <c r="H109" s="6" t="n"/>
-      <c r="I109" s="6" t="n"/>
-      <c r="J109" s="6" t="n"/>
-      <c r="K109" s="6" t="n"/>
-      <c r="L109" s="6" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="7" t="n"/>
-      <c r="B110" s="7" t="n"/>
-      <c r="C110" s="7" t="n"/>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="7" t="n"/>
-      <c r="I110" s="7" t="n"/>
-      <c r="J110" s="7" t="n"/>
-      <c r="K110" s="7" t="n"/>
-      <c r="L110" s="7" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B111" s="6" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="6" t="n"/>
+      <c r="E111" s="6" t="n"/>
+      <c r="F111" s="6" t="n"/>
+      <c r="G111" s="6" t="n"/>
+      <c r="H111" s="6" t="n"/>
+      <c r="I111" s="6" t="n"/>
+      <c r="J111" s="6" t="n"/>
+      <c r="K111" s="6" t="n"/>
+      <c r="L111" s="6" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A112" s="7" t="n"/>
+      <c r="B112" s="7" t="n"/>
+      <c r="C112" s="7" t="n"/>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="7" t="n"/>
+      <c r="F112" s="7" t="n"/>
+      <c r="G112" s="7" t="n"/>
+      <c r="H112" s="7" t="n"/>
+      <c r="I112" s="7" t="n"/>
+      <c r="J112" s="7" t="n"/>
+      <c r="K112" s="7" t="n"/>
+      <c r="L112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -5958,155 +5948,165 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Type minutes-per-unit in the yellow column; blank leaves the minutes columns as "-". Raw counts are in ECONOMY IMPACT above.</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>PACKS PER SOURCE (mean)</t>
         </is>
       </c>
-      <c r="B116" s="6" t="n"/>
-      <c r="C116" s="6" t="n"/>
-      <c r="D116" s="6" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
-      <c r="G116" s="6" t="n"/>
-      <c r="H116" s="6" t="n"/>
-      <c r="I116" s="6" t="n"/>
-      <c r="J116" s="6" t="n"/>
-      <c r="K116" s="6" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="n"/>
-      <c r="B117" s="7" t="n"/>
-      <c r="C117" s="7" t="n"/>
-      <c r="D117" s="7" t="n"/>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="7" t="n"/>
-      <c r="G117" s="7" t="n"/>
-      <c r="H117" s="7" t="n"/>
-      <c r="I117" s="7" t="n"/>
-      <c r="J117" s="7" t="n"/>
-      <c r="K117" s="7" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K118" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="6" t="n"/>
+      <c r="F118" s="6" t="n"/>
+      <c r="G118" s="6" t="n"/>
+      <c r="H118" s="6" t="n"/>
+      <c r="I118" s="6" t="n"/>
+      <c r="J118" s="6" t="n"/>
+      <c r="K118" s="6" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K119" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A119" s="7" t="n"/>
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="7" t="n"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="7" t="n"/>
+      <c r="G119" s="7" t="n"/>
+      <c r="H119" s="7" t="n"/>
+      <c r="I119" s="7" t="n"/>
+      <c r="J119" s="7" t="n"/>
+      <c r="K119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -7704,149 +7704,149 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="149">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr">
         <is>
           <t>PACKS PER SOURCE (p10-p90)</t>
         </is>
       </c>
-      <c r="B149" s="6" t="n"/>
-      <c r="C149" s="6" t="n"/>
-      <c r="D149" s="6" t="n"/>
-      <c r="E149" s="6" t="n"/>
-      <c r="F149" s="6" t="n"/>
-      <c r="G149" s="6" t="n"/>
-      <c r="H149" s="6" t="n"/>
-      <c r="I149" s="6" t="n"/>
-      <c r="J149" s="6" t="n"/>
-      <c r="K149" s="6" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="7" t="n"/>
-      <c r="B150" s="7" t="n"/>
-      <c r="C150" s="7" t="n"/>
-      <c r="D150" s="7" t="n"/>
-      <c r="E150" s="7" t="n"/>
-      <c r="F150" s="7" t="n"/>
-      <c r="G150" s="7" t="n"/>
-      <c r="H150" s="7" t="n"/>
-      <c r="I150" s="7" t="n"/>
-      <c r="J150" s="7" t="n"/>
-      <c r="K150" s="7" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K151" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B151" s="6" t="n"/>
+      <c r="C151" s="6" t="n"/>
+      <c r="D151" s="6" t="n"/>
+      <c r="E151" s="6" t="n"/>
+      <c r="F151" s="6" t="n"/>
+      <c r="G151" s="6" t="n"/>
+      <c r="H151" s="6" t="n"/>
+      <c r="I151" s="6" t="n"/>
+      <c r="J151" s="6" t="n"/>
+      <c r="K151" s="6" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K152" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A152" s="7" t="n"/>
+      <c r="B152" s="7" t="n"/>
+      <c r="C152" s="7" t="n"/>
+      <c r="D152" s="7" t="n"/>
+      <c r="E152" s="7" t="n"/>
+      <c r="F152" s="7" t="n"/>
+      <c r="G152" s="7" t="n"/>
+      <c r="H152" s="7" t="n"/>
+      <c r="I152" s="7" t="n"/>
+      <c r="J152" s="7" t="n"/>
+      <c r="K152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
@@ -9444,149 +9444,149 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="182">
-      <c r="A182" s="5" t="inlineStr">
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
         <is>
           <t>CARDS PER SOURCE (mean)</t>
         </is>
       </c>
-      <c r="B182" s="6" t="n"/>
-      <c r="C182" s="6" t="n"/>
-      <c r="D182" s="6" t="n"/>
-      <c r="E182" s="6" t="n"/>
-      <c r="F182" s="6" t="n"/>
-      <c r="G182" s="6" t="n"/>
-      <c r="H182" s="6" t="n"/>
-      <c r="I182" s="6" t="n"/>
-      <c r="J182" s="6" t="n"/>
-      <c r="K182" s="6" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="7" t="n"/>
-      <c r="B183" s="7" t="n"/>
-      <c r="C183" s="7" t="n"/>
-      <c r="D183" s="7" t="n"/>
-      <c r="E183" s="7" t="n"/>
-      <c r="F183" s="7" t="n"/>
-      <c r="G183" s="7" t="n"/>
-      <c r="H183" s="7" t="n"/>
-      <c r="I183" s="7" t="n"/>
-      <c r="J183" s="7" t="n"/>
-      <c r="K183" s="7" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K184" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="6" t="n"/>
+      <c r="F184" s="6" t="n"/>
+      <c r="G184" s="6" t="n"/>
+      <c r="H184" s="6" t="n"/>
+      <c r="I184" s="6" t="n"/>
+      <c r="J184" s="6" t="n"/>
+      <c r="K184" s="6" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K185" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A185" s="7" t="n"/>
+      <c r="B185" s="7" t="n"/>
+      <c r="C185" s="7" t="n"/>
+      <c r="D185" s="7" t="n"/>
+      <c r="E185" s="7" t="n"/>
+      <c r="F185" s="7" t="n"/>
+      <c r="G185" s="7" t="n"/>
+      <c r="H185" s="7" t="n"/>
+      <c r="I185" s="7" t="n"/>
+      <c r="J185" s="7" t="n"/>
+      <c r="K185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="8" t="inlineStr">
@@ -11184,149 +11184,149 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="inlineStr">
         <is>
           <t>CARDS PER SOURCE (p10-p90)</t>
         </is>
       </c>
-      <c r="B215" s="6" t="n"/>
-      <c r="C215" s="6" t="n"/>
-      <c r="D215" s="6" t="n"/>
-      <c r="E215" s="6" t="n"/>
-      <c r="F215" s="6" t="n"/>
-      <c r="G215" s="6" t="n"/>
-      <c r="H215" s="6" t="n"/>
-      <c r="I215" s="6" t="n"/>
-      <c r="J215" s="6" t="n"/>
-      <c r="K215" s="6" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="7" t="n"/>
-      <c r="B216" s="7" t="n"/>
-      <c r="C216" s="7" t="n"/>
-      <c r="D216" s="7" t="n"/>
-      <c r="E216" s="7" t="n"/>
-      <c r="F216" s="7" t="n"/>
-      <c r="G216" s="7" t="n"/>
-      <c r="H216" s="7" t="n"/>
-      <c r="I216" s="7" t="n"/>
-      <c r="J216" s="7" t="n"/>
-      <c r="K216" s="7" t="n"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K217" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B217" s="6" t="n"/>
+      <c r="C217" s="6" t="n"/>
+      <c r="D217" s="6" t="n"/>
+      <c r="E217" s="6" t="n"/>
+      <c r="F217" s="6" t="n"/>
+      <c r="G217" s="6" t="n"/>
+      <c r="H217" s="6" t="n"/>
+      <c r="I217" s="6" t="n"/>
+      <c r="J217" s="6" t="n"/>
+      <c r="K217" s="6" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K218" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A218" s="7" t="n"/>
+      <c r="B218" s="7" t="n"/>
+      <c r="C218" s="7" t="n"/>
+      <c r="D218" s="7" t="n"/>
+      <c r="E218" s="7" t="n"/>
+      <c r="F218" s="7" t="n"/>
+      <c r="G218" s="7" t="n"/>
+      <c r="H218" s="7" t="n"/>
+      <c r="I218" s="7" t="n"/>
+      <c r="J218" s="7" t="n"/>
+      <c r="K218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="8" t="inlineStr">
@@ -12924,52 +12924,173 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="248">
-      <c r="A248" s="5" t="inlineStr">
+      <c r="A248" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="B248" s="6" t="n"/>
-      <c r="C248" s="6" t="n"/>
-      <c r="D248" s="6" t="n"/>
-      <c r="E248" s="6" t="n"/>
-      <c r="F248" s="6" t="n"/>
-      <c r="G248" s="6" t="n"/>
-      <c r="H248" s="6" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="4" t="inlineStr">
-        <is>
-          <t>Ranges are p10-p90 ACROSS PLAYERS, not min-max: with 50 players the true extremes are single outliers that move every run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="4" t="inlineStr">
-        <is>
-          <t>Cadence is per CALENDAR day (all 33), including days the player did not play — so the permutations stay comparable.</t>
-        </is>
-      </c>
+      <c r="B250" s="6" t="n"/>
+      <c r="C250" s="6" t="n"/>
+      <c r="D250" s="6" t="n"/>
+      <c r="E250" s="6" t="n"/>
+      <c r="F250" s="6" t="n"/>
+      <c r="G250" s="6" t="n"/>
+      <c r="H250" s="6" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>ECONOMY IMPACT is what the collection feature PAYS OUT (SET + ALBUM REWARDS). It is not the segment's whole economy.</t>
+          <t>Ranges are p10-p90 ACROSS PLAYERS, not min-max: with 50 players the true extremes are single outliers that move every run.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>A zero in a per-source row is a finding, not a gap — e.g. Kite Festival at its assumed 0.35 opt-in, or a ladder with no pack authored on it.</t>
+          <t>Cadence is per CALENDAR day (all 33), including days the player did not play, so the permutations stay comparable. Col_Cards_Daily counts the SAME season over the 4-6 days that actually dropped a pack, which is why its log reads 2-3 packs a day against 0.35 here. "Days with a pack" x "Packs on a day that has one" = Total Packs Opened, above.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
+          <t>ECONOMY IMPACT is what the collection feature PAYS OUT (SET + ALBUM REWARDS). It is not the segment's whole economy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>A zero in a per-source row is a finding, not a gap — e.g. Kite Festival at its assumed 0.35 opt-in, or a ladder with no pack authored on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
           <t>"A. 0" is absent by design: data_seg_beh has no row for it, so nothing can price its reach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Envelopes are priced off the _v2 ladders ONLY, in the 1-star Dly .. 6-star Dly columns. A pack typed on a base sheet, or under any other column heading, moves nothing here. On a LEADERBOARD the top rows are ranks 1-3, which a mid segment reaches ~5% of the time: a pack put there is worth ~0.006 packs a season.</t>
         </is>
       </c>
     </row>

--- a/display/Col_Cards_Totals_v1.xlsx
+++ b/display/Col_Cards_Totals_v1.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L256"/>
+  <dimension ref="A1:L258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1741,7 +1741,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>CADENCE (per calendar day, all 33)</t>
+          <t>CADENCE (packs per day, three denominators)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n"/>
@@ -2110,149 +2110,149 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>ECONOMY IMPACT - TOTAL (mean per player)</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="6" t="n"/>
-      <c r="I39" s="6" t="n"/>
-      <c r="J39" s="6" t="n"/>
-      <c r="K39" s="6" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n"/>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="7" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K41" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="6" t="n"/>
+      <c r="J41" s="6" t="n"/>
+      <c r="K41" s="6" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -3337,149 +3337,149 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>ECONOMY IMPACT - FROM SET COMPLETIONS</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="6" t="n"/>
-      <c r="I63" s="6" t="n"/>
-      <c r="J63" s="6" t="n"/>
-      <c r="K63" s="6" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n"/>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-      <c r="J64" s="7" t="n"/>
-      <c r="K64" s="7" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="n"/>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="6" t="n"/>
+      <c r="J65" s="6" t="n"/>
+      <c r="K65" s="6" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A66" s="7" t="n"/>
+      <c r="B66" s="7" t="n"/>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+      <c r="I66" s="7" t="n"/>
+      <c r="J66" s="7" t="n"/>
+      <c r="K66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -4564,149 +4564,149 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>ECONOMY IMPACT - FROM ALBUM COMPLETIONS</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="6" t="n"/>
-      <c r="H87" s="6" t="n"/>
-      <c r="I87" s="6" t="n"/>
-      <c r="J87" s="6" t="n"/>
-      <c r="K87" s="6" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="n"/>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
-      <c r="G88" s="7" t="n"/>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
-      <c r="J88" s="7" t="n"/>
-      <c r="K88" s="7" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K89" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="n"/>
+      <c r="G89" s="6" t="n"/>
+      <c r="H89" s="6" t="n"/>
+      <c r="I89" s="6" t="n"/>
+      <c r="J89" s="6" t="n"/>
+      <c r="K89" s="6" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K90" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A90" s="7" t="n"/>
+      <c r="B90" s="7" t="n"/>
+      <c r="C90" s="7" t="n"/>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="7" t="n"/>
+      <c r="F90" s="7" t="n"/>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="7" t="n"/>
+      <c r="I90" s="7" t="n"/>
+      <c r="J90" s="7" t="n"/>
+      <c r="K90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -5791,161 +5791,151 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>UNLIMITED BOOSTERS IN MINUTES</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-      <c r="E111" s="6" t="n"/>
-      <c r="F111" s="6" t="n"/>
-      <c r="G111" s="6" t="n"/>
-      <c r="H111" s="6" t="n"/>
-      <c r="I111" s="6" t="n"/>
-      <c r="J111" s="6" t="n"/>
-      <c r="K111" s="6" t="n"/>
-      <c r="L111" s="6" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="7" t="n"/>
-      <c r="B112" s="7" t="n"/>
-      <c r="C112" s="7" t="n"/>
-      <c r="D112" s="7" t="n"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="7" t="n"/>
-      <c r="G112" s="7" t="n"/>
-      <c r="H112" s="7" t="n"/>
-      <c r="I112" s="7" t="n"/>
-      <c r="J112" s="7" t="n"/>
-      <c r="K112" s="7" t="n"/>
-      <c r="L112" s="7" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+      <c r="E113" s="6" t="n"/>
+      <c r="F113" s="6" t="n"/>
+      <c r="G113" s="6" t="n"/>
+      <c r="H113" s="6" t="n"/>
+      <c r="I113" s="6" t="n"/>
+      <c r="J113" s="6" t="n"/>
+      <c r="K113" s="6" t="n"/>
+      <c r="L113" s="6" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A114" s="7" t="n"/>
+      <c r="B114" s="7" t="n"/>
+      <c r="C114" s="7" t="n"/>
+      <c r="D114" s="7" t="n"/>
+      <c r="E114" s="7" t="n"/>
+      <c r="F114" s="7" t="n"/>
+      <c r="G114" s="7" t="n"/>
+      <c r="H114" s="7" t="n"/>
+      <c r="I114" s="7" t="n"/>
+      <c r="J114" s="7" t="n"/>
+      <c r="K114" s="7" t="n"/>
+      <c r="L114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -6072,155 +6062,165 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>Type minutes-per-unit in the yellow column; blank leaves the minutes columns as "-". Raw counts are in ECONOMY IMPACT above.</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>PACKS PER SOURCE (mean)</t>
         </is>
       </c>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="6" t="n"/>
-      <c r="H118" s="6" t="n"/>
-      <c r="I118" s="6" t="n"/>
-      <c r="J118" s="6" t="n"/>
-      <c r="K118" s="6" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="7" t="n"/>
-      <c r="B119" s="7" t="n"/>
-      <c r="C119" s="7" t="n"/>
-      <c r="D119" s="7" t="n"/>
-      <c r="E119" s="7" t="n"/>
-      <c r="F119" s="7" t="n"/>
-      <c r="G119" s="7" t="n"/>
-      <c r="H119" s="7" t="n"/>
-      <c r="I119" s="7" t="n"/>
-      <c r="J119" s="7" t="n"/>
-      <c r="K119" s="7" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K120" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B120" s="6" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+      <c r="E120" s="6" t="n"/>
+      <c r="F120" s="6" t="n"/>
+      <c r="G120" s="6" t="n"/>
+      <c r="H120" s="6" t="n"/>
+      <c r="I120" s="6" t="n"/>
+      <c r="J120" s="6" t="n"/>
+      <c r="K120" s="6" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K121" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A121" s="7" t="n"/>
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="7" t="n"/>
+      <c r="G121" s="7" t="n"/>
+      <c r="H121" s="7" t="n"/>
+      <c r="I121" s="7" t="n"/>
+      <c r="J121" s="7" t="n"/>
+      <c r="K121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
@@ -7818,149 +7818,149 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>PACKS PER SOURCE (p10-p90)</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="F151" s="6" t="n"/>
-      <c r="G151" s="6" t="n"/>
-      <c r="H151" s="6" t="n"/>
-      <c r="I151" s="6" t="n"/>
-      <c r="J151" s="6" t="n"/>
-      <c r="K151" s="6" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="7" t="n"/>
-      <c r="B152" s="7" t="n"/>
-      <c r="C152" s="7" t="n"/>
-      <c r="D152" s="7" t="n"/>
-      <c r="E152" s="7" t="n"/>
-      <c r="F152" s="7" t="n"/>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="7" t="n"/>
-      <c r="I152" s="7" t="n"/>
-      <c r="J152" s="7" t="n"/>
-      <c r="K152" s="7" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K153" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B153" s="6" t="n"/>
+      <c r="C153" s="6" t="n"/>
+      <c r="D153" s="6" t="n"/>
+      <c r="E153" s="6" t="n"/>
+      <c r="F153" s="6" t="n"/>
+      <c r="G153" s="6" t="n"/>
+      <c r="H153" s="6" t="n"/>
+      <c r="I153" s="6" t="n"/>
+      <c r="J153" s="6" t="n"/>
+      <c r="K153" s="6" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K154" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A154" s="7" t="n"/>
+      <c r="B154" s="7" t="n"/>
+      <c r="C154" s="7" t="n"/>
+      <c r="D154" s="7" t="n"/>
+      <c r="E154" s="7" t="n"/>
+      <c r="F154" s="7" t="n"/>
+      <c r="G154" s="7" t="n"/>
+      <c r="H154" s="7" t="n"/>
+      <c r="I154" s="7" t="n"/>
+      <c r="J154" s="7" t="n"/>
+      <c r="K154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
@@ -9558,149 +9558,149 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="A184" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t>CARDS PER SOURCE (mean)</t>
         </is>
       </c>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="6" t="n"/>
-      <c r="D184" s="6" t="n"/>
-      <c r="E184" s="6" t="n"/>
-      <c r="F184" s="6" t="n"/>
-      <c r="G184" s="6" t="n"/>
-      <c r="H184" s="6" t="n"/>
-      <c r="I184" s="6" t="n"/>
-      <c r="J184" s="6" t="n"/>
-      <c r="K184" s="6" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="7" t="n"/>
-      <c r="B185" s="7" t="n"/>
-      <c r="C185" s="7" t="n"/>
-      <c r="D185" s="7" t="n"/>
-      <c r="E185" s="7" t="n"/>
-      <c r="F185" s="7" t="n"/>
-      <c r="G185" s="7" t="n"/>
-      <c r="H185" s="7" t="n"/>
-      <c r="I185" s="7" t="n"/>
-      <c r="J185" s="7" t="n"/>
-      <c r="K185" s="7" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K186" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B186" s="6" t="n"/>
+      <c r="C186" s="6" t="n"/>
+      <c r="D186" s="6" t="n"/>
+      <c r="E186" s="6" t="n"/>
+      <c r="F186" s="6" t="n"/>
+      <c r="G186" s="6" t="n"/>
+      <c r="H186" s="6" t="n"/>
+      <c r="I186" s="6" t="n"/>
+      <c r="J186" s="6" t="n"/>
+      <c r="K186" s="6" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K187" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A187" s="7" t="n"/>
+      <c r="B187" s="7" t="n"/>
+      <c r="C187" s="7" t="n"/>
+      <c r="D187" s="7" t="n"/>
+      <c r="E187" s="7" t="n"/>
+      <c r="F187" s="7" t="n"/>
+      <c r="G187" s="7" t="n"/>
+      <c r="H187" s="7" t="n"/>
+      <c r="I187" s="7" t="n"/>
+      <c r="J187" s="7" t="n"/>
+      <c r="K187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="8" t="inlineStr">
@@ -11298,149 +11298,149 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="217">
-      <c r="A217" s="5" t="inlineStr">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="5" t="inlineStr">
         <is>
           <t>CARDS PER SOURCE (p10-p90)</t>
         </is>
       </c>
-      <c r="B217" s="6" t="n"/>
-      <c r="C217" s="6" t="n"/>
-      <c r="D217" s="6" t="n"/>
-      <c r="E217" s="6" t="n"/>
-      <c r="F217" s="6" t="n"/>
-      <c r="G217" s="6" t="n"/>
-      <c r="H217" s="6" t="n"/>
-      <c r="I217" s="6" t="n"/>
-      <c r="J217" s="6" t="n"/>
-      <c r="K217" s="6" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="7" t="n"/>
-      <c r="B218" s="7" t="n"/>
-      <c r="C218" s="7" t="n"/>
-      <c r="D218" s="7" t="n"/>
-      <c r="E218" s="7" t="n"/>
-      <c r="F218" s="7" t="n"/>
-      <c r="G218" s="7" t="n"/>
-      <c r="H218" s="7" t="n"/>
-      <c r="I218" s="7" t="n"/>
-      <c r="J218" s="7" t="n"/>
-      <c r="K218" s="7" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K219" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="B219" s="6" t="n"/>
+      <c r="C219" s="6" t="n"/>
+      <c r="D219" s="6" t="n"/>
+      <c r="E219" s="6" t="n"/>
+      <c r="F219" s="6" t="n"/>
+      <c r="G219" s="6" t="n"/>
+      <c r="H219" s="6" t="n"/>
+      <c r="I219" s="6" t="n"/>
+      <c r="J219" s="6" t="n"/>
+      <c r="K219" s="6" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K220" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="A220" s="7" t="n"/>
+      <c r="B220" s="7" t="n"/>
+      <c r="C220" s="7" t="n"/>
+      <c r="D220" s="7" t="n"/>
+      <c r="E220" s="7" t="n"/>
+      <c r="F220" s="7" t="n"/>
+      <c r="G220" s="7" t="n"/>
+      <c r="H220" s="7" t="n"/>
+      <c r="I220" s="7" t="n"/>
+      <c r="J220" s="7" t="n"/>
+      <c r="K220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="8" t="inlineStr">
@@ -13038,57 +13038,171 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
     <row r="250">
-      <c r="A250" s="5" t="inlineStr">
+      <c r="A250" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
-      <c r="B250" s="6" t="n"/>
-      <c r="C250" s="6" t="n"/>
-      <c r="D250" s="6" t="n"/>
-      <c r="E250" s="6" t="n"/>
-      <c r="F250" s="6" t="n"/>
-      <c r="G250" s="6" t="n"/>
-      <c r="H250" s="6" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>Ranges are p10-p90 ACROSS PLAYERS, not min-max: with 50 players the true extremes are single outliers that move every run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="4" t="inlineStr">
-        <is>
-          <t>Cadence is per CALENDAR day (all 33), including days the player did not play, so the permutations stay comparable. Col_Cards_Daily counts the SAME season over the 4-6 days that actually dropped a pack, which is why its log reads 2-3 packs a day against 0.35 here. "Days with a pack" x "Packs on a day that has one" = Total Packs Opened, above.</t>
-        </is>
-      </c>
+      <c r="B252" s="6" t="n"/>
+      <c r="C252" s="6" t="n"/>
+      <c r="D252" s="6" t="n"/>
+      <c r="E252" s="6" t="n"/>
+      <c r="F252" s="6" t="n"/>
+      <c r="G252" s="6" t="n"/>
+      <c r="H252" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>ECONOMY IMPACT is what the collection feature PAYS OUT (SET + ALBUM REWARDS). It is not the segment's whole economy.</t>
+          <t>Ranges are p10-p90 ACROSS PLAYERS, not min-max: with 50 players the true extremes are single outliers that move every run.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>A zero in a per-source row is a finding, not a gap — e.g. Kite Festival at its assumed 0.35 opt-in, or a ladder with no pack authored on it.</t>
+          <t>CADENCE gives three per-day rates because "packs per day" has three denominators: all 33 calendar days (comparable across segments, carries attendance in it), the days the player actually played (the pacing number), and the days that dropped anything (what the Col_Cards_Daily log reads like, because packs clump). Both denominators are on the sheet, so each rate x its day count = Total Packs Opened, above.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>"A. 0" is absent by design: data_seg_beh has no row for it, so nothing can price its reach.</t>
+          <t>ECONOMY IMPACT is what the collection feature PAYS OUT (SET + ALBUM REWARDS). It is not the segment's whole economy.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>A zero in a per-source row is a finding, not a gap — e.g. Kite Festival at its assumed 0.35 opt-in, or a ladder with no pack authored on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>"A. 0" is absent by design: data_seg_beh has no row for it, so nothing can price its reach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>Envelopes are priced off the _v2 ladders ONLY, in the 1-star Dly .. 6-star Dly columns. A pack typed on a base sheet, or under any other column heading, moves nothing here. On a LEADERBOARD the top rows are ranks 1-3, which a mid segment reaches ~5% of the time: a pack put there is worth ~0.006 packs a season.</t>
         </is>
